--- a/data/excel/价格分析.xlsx
+++ b/data/excel/价格分析.xlsx
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -565,39 +565,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>纯电动</t>
+          <t>燃油</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>14.68</v>
+        <v>13.83</v>
       </c>
       <c r="D3" t="n">
-        <v>19.69</v>
+        <v>21.61</v>
       </c>
       <c r="E3" t="n">
-        <v>17.18</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>燃油</t>
+          <t>纯电动</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>12.88</v>
+        <v>14.68</v>
       </c>
       <c r="D4" t="n">
-        <v>20.58</v>
+        <v>19.69</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="5">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>9.43</v>
+        <v>11.14</v>
       </c>
       <c r="D5" t="n">
-        <v>13.08</v>
+        <v>15.7</v>
       </c>
       <c r="E5" t="n">
-        <v>11.26</v>
+        <v>13.42</v>
       </c>
     </row>
   </sheetData>
